--- a/docs/Project Plan.xlsx
+++ b/docs/Project Plan.xlsx
@@ -391,92 +391,96 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="8" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="8" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -732,1092 +736,1092 @@
   <dimension ref="A1:R51"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="92.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="10.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="118.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="10.16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-    </row>
-    <row r="2" s="8" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="5" t="n">
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+    </row>
+    <row r="2" s="9" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="5" t="n">
+      <c r="D2" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="E2" s="5" t="n">
+      <c r="E2" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F2" s="6" t="n">
+      <c r="F2" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="G2" s="6" t="n">
+      <c r="G2" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="H2" s="6" t="n">
+      <c r="H2" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="I2" s="6" t="n">
+      <c r="I2" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="J2" s="6" t="n">
+      <c r="J2" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="K2" s="6" t="n">
+      <c r="K2" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="L2" s="6" t="n">
+      <c r="L2" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="M2" s="7" t="n">
+      <c r="M2" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="N2" s="7" t="n">
+      <c r="N2" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="O2" s="7" t="n">
+      <c r="O2" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="R2" s="0"/>
+      <c r="R2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9" t="n">
+      <c r="A3" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="11"/>
-      <c r="O3" s="11"/>
-      <c r="Q3" s="0" t="s">
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+      <c r="L3" s="12"/>
+      <c r="M3" s="12"/>
+      <c r="N3" s="12"/>
+      <c r="O3" s="12"/>
+      <c r="Q3" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9"/>
-      <c r="B4" s="12" t="s">
+      <c r="A4" s="10"/>
+      <c r="B4" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="11"/>
-      <c r="O4" s="11"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
+      <c r="L4" s="12"/>
+      <c r="M4" s="12"/>
+      <c r="N4" s="12"/>
+      <c r="O4" s="12"/>
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9"/>
-      <c r="B5" s="10" t="s">
+      <c r="A5" s="10"/>
+      <c r="B5" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="11"/>
-      <c r="N5" s="11"/>
-      <c r="O5" s="11"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="12"/>
+      <c r="N5" s="12"/>
+      <c r="O5" s="12"/>
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9"/>
-      <c r="B6" s="12" t="s">
+      <c r="A6" s="10"/>
+      <c r="B6" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11"/>
-      <c r="N6" s="11"/>
-      <c r="O6" s="11"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
+      <c r="N6" s="12"/>
+      <c r="O6" s="12"/>
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9"/>
-      <c r="B7" s="12" t="s">
+      <c r="A7" s="10"/>
+      <c r="B7" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="11"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="11"/>
-      <c r="N7" s="11"/>
-      <c r="O7" s="11"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="12"/>
+      <c r="L7" s="12"/>
+      <c r="M7" s="12"/>
+      <c r="N7" s="12"/>
+      <c r="O7" s="12"/>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9"/>
-      <c r="B8" s="10" t="s">
+      <c r="A8" s="10"/>
+      <c r="B8" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="11"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="11"/>
-      <c r="N8" s="11"/>
-      <c r="O8" s="11"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="12"/>
+      <c r="N8" s="12"/>
+      <c r="O8" s="12"/>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9"/>
-      <c r="B9" s="12" t="s">
+      <c r="A9" s="10"/>
+      <c r="B9" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="11"/>
-      <c r="L9" s="11"/>
-      <c r="M9" s="11"/>
-      <c r="N9" s="11"/>
-      <c r="O9" s="11"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="12"/>
+      <c r="M9" s="12"/>
+      <c r="N9" s="12"/>
+      <c r="O9" s="12"/>
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9"/>
-      <c r="B10" s="12" t="s">
+      <c r="A10" s="10"/>
+      <c r="B10" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="14" t="s">
+      <c r="C10" s="12"/>
+      <c r="D10" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="11"/>
-      <c r="N10" s="11"/>
-      <c r="O10" s="11"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="12"/>
+      <c r="L10" s="12"/>
+      <c r="M10" s="12"/>
+      <c r="N10" s="12"/>
+      <c r="O10" s="12"/>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9"/>
-      <c r="B11" s="12" t="s">
+      <c r="A11" s="10"/>
+      <c r="B11" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="14" t="s">
+      <c r="C11" s="12"/>
+      <c r="D11" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="14"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="11"/>
-      <c r="O11" s="11"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
+      <c r="L11" s="12"/>
+      <c r="M11" s="12"/>
+      <c r="N11" s="12"/>
+      <c r="O11" s="12"/>
     </row>
     <row r="12" customFormat="false" ht="33" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="9"/>
-      <c r="B12" s="15" t="s">
+      <c r="A12" s="10"/>
+      <c r="B12" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="14" t="s">
+      <c r="C12" s="12"/>
+      <c r="D12" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="11"/>
-      <c r="O12" s="11"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
+      <c r="L12" s="12"/>
+      <c r="M12" s="12"/>
+      <c r="N12" s="12"/>
+      <c r="O12" s="12"/>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="9"/>
-      <c r="B13" s="12" t="s">
+      <c r="A13" s="10"/>
+      <c r="B13" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="11"/>
-      <c r="D13" s="14" t="s">
+      <c r="C13" s="12"/>
+      <c r="D13" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="11"/>
-      <c r="L13" s="11"/>
-      <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
-      <c r="O13" s="11"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="12"/>
+      <c r="L13" s="12"/>
+      <c r="M13" s="12"/>
+      <c r="N13" s="12"/>
+      <c r="O13" s="12"/>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="9"/>
-      <c r="B14" s="10" t="s">
+      <c r="A14" s="10"/>
+      <c r="B14" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="11"/>
-      <c r="N14" s="11"/>
-      <c r="O14" s="11"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12"/>
+      <c r="L14" s="12"/>
+      <c r="M14" s="12"/>
+      <c r="N14" s="12"/>
+      <c r="O14" s="12"/>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="9"/>
-      <c r="B15" s="12" t="s">
+      <c r="A15" s="10"/>
+      <c r="B15" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="C15" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="11"/>
-      <c r="N15" s="11"/>
-      <c r="O15" s="11"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="12"/>
+      <c r="L15" s="12"/>
+      <c r="M15" s="12"/>
+      <c r="N15" s="12"/>
+      <c r="O15" s="12"/>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="9"/>
-      <c r="B16" s="12" t="s">
+      <c r="A16" s="10"/>
+      <c r="B16" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="11"/>
-      <c r="D16" s="14" t="s">
+      <c r="C16" s="12"/>
+      <c r="D16" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="11"/>
-      <c r="N16" s="11"/>
-      <c r="O16" s="11"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="12"/>
+      <c r="L16" s="12"/>
+      <c r="M16" s="12"/>
+      <c r="N16" s="12"/>
+      <c r="O16" s="12"/>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="9"/>
-      <c r="B17" s="10" t="s">
+      <c r="A17" s="10"/>
+      <c r="B17" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="11"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="11"/>
-      <c r="N17" s="11"/>
-      <c r="O17" s="11"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="12"/>
+      <c r="K17" s="12"/>
+      <c r="L17" s="12"/>
+      <c r="M17" s="12"/>
+      <c r="N17" s="12"/>
+      <c r="O17" s="12"/>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="9"/>
-      <c r="B18" s="12" t="s">
+      <c r="A18" s="10"/>
+      <c r="B18" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="14" t="s">
+      <c r="C18" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="11"/>
-      <c r="J18" s="11"/>
-      <c r="K18" s="11"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="11"/>
-      <c r="N18" s="11"/>
-      <c r="O18" s="11"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="12"/>
+      <c r="M18" s="12"/>
+      <c r="N18" s="12"/>
+      <c r="O18" s="12"/>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="16" t="n">
+      <c r="A19" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="17"/>
-      <c r="I19" s="17"/>
-      <c r="J19" s="17"/>
-      <c r="K19" s="17"/>
-      <c r="L19" s="17"/>
-      <c r="M19" s="17"/>
-      <c r="N19" s="17"/>
-      <c r="O19" s="17"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="18"/>
+      <c r="J19" s="18"/>
+      <c r="K19" s="18"/>
+      <c r="L19" s="18"/>
+      <c r="M19" s="18"/>
+      <c r="N19" s="18"/>
+      <c r="O19" s="18"/>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="16"/>
-      <c r="B20" s="12" t="s">
+      <c r="A20" s="17"/>
+      <c r="B20" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="18" t="s">
+      <c r="C20" s="18"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="G20" s="18"/>
-      <c r="H20" s="18"/>
-      <c r="I20" s="18"/>
-      <c r="J20" s="18"/>
-      <c r="K20" s="18"/>
-      <c r="L20" s="18"/>
-      <c r="M20" s="18"/>
-      <c r="N20" s="17"/>
-      <c r="O20" s="17"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="19"/>
+      <c r="K20" s="19"/>
+      <c r="L20" s="19"/>
+      <c r="M20" s="19"/>
+      <c r="N20" s="18"/>
+      <c r="O20" s="18"/>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="16"/>
-      <c r="B21" s="12" t="s">
+      <c r="A21" s="17"/>
+      <c r="B21" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="13" t="s">
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="17"/>
-      <c r="J21" s="17"/>
-      <c r="K21" s="17"/>
-      <c r="L21" s="17"/>
-      <c r="M21" s="17"/>
-      <c r="N21" s="17"/>
-      <c r="O21" s="17"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="18"/>
+      <c r="J21" s="18"/>
+      <c r="K21" s="18"/>
+      <c r="L21" s="18"/>
+      <c r="M21" s="18"/>
+      <c r="N21" s="18"/>
+      <c r="O21" s="18"/>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="16"/>
-      <c r="B22" s="12" t="s">
+      <c r="A22" s="17"/>
+      <c r="B22" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="13" t="s">
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="17"/>
-      <c r="J22" s="17"/>
-      <c r="K22" s="17"/>
-      <c r="L22" s="17"/>
-      <c r="M22" s="17"/>
-      <c r="N22" s="17"/>
-      <c r="O22" s="17"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="18"/>
+      <c r="J22" s="18"/>
+      <c r="K22" s="18"/>
+      <c r="L22" s="18"/>
+      <c r="M22" s="18"/>
+      <c r="N22" s="18"/>
+      <c r="O22" s="18"/>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="16"/>
-      <c r="B23" s="12" t="s">
+      <c r="A23" s="17"/>
+      <c r="B23" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="13" t="s">
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="I23" s="13"/>
-      <c r="J23" s="13"/>
-      <c r="K23" s="17"/>
-      <c r="L23" s="17"/>
-      <c r="M23" s="17"/>
-      <c r="N23" s="17"/>
-      <c r="O23" s="17"/>
-      <c r="Q23" s="19"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="14"/>
+      <c r="K23" s="18"/>
+      <c r="L23" s="18"/>
+      <c r="M23" s="18"/>
+      <c r="N23" s="18"/>
+      <c r="O23" s="18"/>
+      <c r="Q23" s="20"/>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="16"/>
-      <c r="B24" s="12" t="s">
+      <c r="A24" s="17"/>
+      <c r="B24" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="13" t="s">
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="I24" s="13"/>
-      <c r="J24" s="13"/>
-      <c r="K24" s="17"/>
-      <c r="L24" s="17"/>
-      <c r="M24" s="17"/>
-      <c r="N24" s="17"/>
-      <c r="O24" s="17"/>
-      <c r="Q24" s="19"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="18"/>
+      <c r="L24" s="18"/>
+      <c r="M24" s="18"/>
+      <c r="N24" s="18"/>
+      <c r="O24" s="18"/>
+      <c r="Q24" s="20"/>
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="16"/>
-      <c r="B25" s="10" t="s">
+      <c r="A25" s="17"/>
+      <c r="B25" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="17"/>
-      <c r="I25" s="17"/>
-      <c r="J25" s="17"/>
-      <c r="K25" s="17"/>
-      <c r="L25" s="17"/>
-      <c r="M25" s="17"/>
-      <c r="N25" s="17"/>
-      <c r="O25" s="17"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="18"/>
+      <c r="J25" s="18"/>
+      <c r="K25" s="18"/>
+      <c r="L25" s="18"/>
+      <c r="M25" s="18"/>
+      <c r="N25" s="18"/>
+      <c r="O25" s="18"/>
     </row>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="16"/>
-      <c r="B26" s="12" t="s">
+      <c r="A26" s="17"/>
+      <c r="B26" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="13" t="s">
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
+      <c r="H26" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="I26" s="13"/>
-      <c r="J26" s="13"/>
-      <c r="K26" s="17"/>
-      <c r="L26" s="17"/>
-      <c r="M26" s="17"/>
-      <c r="N26" s="17"/>
-      <c r="O26" s="17"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="14"/>
+      <c r="K26" s="18"/>
+      <c r="L26" s="18"/>
+      <c r="M26" s="18"/>
+      <c r="N26" s="18"/>
+      <c r="O26" s="18"/>
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="16"/>
-      <c r="B27" s="12" t="s">
+      <c r="A27" s="17"/>
+      <c r="B27" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="17"/>
-      <c r="H27" s="13" t="s">
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="18"/>
+      <c r="H27" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="I27" s="13"/>
-      <c r="J27" s="13"/>
-      <c r="K27" s="17"/>
-      <c r="L27" s="17"/>
-      <c r="M27" s="17"/>
-      <c r="N27" s="17"/>
-      <c r="O27" s="17"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="14"/>
+      <c r="K27" s="18"/>
+      <c r="L27" s="18"/>
+      <c r="M27" s="18"/>
+      <c r="N27" s="18"/>
+      <c r="O27" s="18"/>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="16"/>
-      <c r="B28" s="10" t="s">
+      <c r="A28" s="17"/>
+      <c r="B28" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="17"/>
-      <c r="H28" s="17"/>
-      <c r="I28" s="17"/>
-      <c r="J28" s="17"/>
-      <c r="K28" s="17"/>
-      <c r="L28" s="17"/>
-      <c r="M28" s="17"/>
-      <c r="N28" s="17"/>
-      <c r="O28" s="17"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="18"/>
+      <c r="J28" s="18"/>
+      <c r="K28" s="18"/>
+      <c r="L28" s="18"/>
+      <c r="M28" s="18"/>
+      <c r="N28" s="18"/>
+      <c r="O28" s="18"/>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="16"/>
-      <c r="B29" s="12" t="s">
+      <c r="A29" s="17"/>
+      <c r="B29" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="13" t="s">
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="13"/>
-      <c r="J29" s="13"/>
-      <c r="K29" s="13"/>
-      <c r="L29" s="17"/>
-      <c r="M29" s="17"/>
-      <c r="N29" s="17"/>
-      <c r="O29" s="17"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="14"/>
+      <c r="K29" s="14"/>
+      <c r="L29" s="18"/>
+      <c r="M29" s="18"/>
+      <c r="N29" s="18"/>
+      <c r="O29" s="18"/>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="16"/>
-      <c r="B30" s="12" t="s">
+      <c r="A30" s="17"/>
+      <c r="B30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="13" t="s">
+      <c r="C30" s="18"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="13"/>
-      <c r="I30" s="13"/>
-      <c r="J30" s="13"/>
-      <c r="K30" s="13"/>
-      <c r="L30" s="13"/>
-      <c r="M30" s="17"/>
-      <c r="N30" s="17"/>
-      <c r="O30" s="17"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
+      <c r="K30" s="14"/>
+      <c r="L30" s="14"/>
+      <c r="M30" s="18"/>
+      <c r="N30" s="18"/>
+      <c r="O30" s="18"/>
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="16"/>
-      <c r="B31" s="10" t="s">
+      <c r="A31" s="17"/>
+      <c r="B31" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="17"/>
-      <c r="H31" s="17"/>
-      <c r="I31" s="17"/>
-      <c r="J31" s="17"/>
-      <c r="K31" s="17"/>
-      <c r="L31" s="17"/>
-      <c r="M31" s="17"/>
-      <c r="N31" s="17"/>
-      <c r="O31" s="17"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="18"/>
+      <c r="H31" s="18"/>
+      <c r="I31" s="18"/>
+      <c r="J31" s="18"/>
+      <c r="K31" s="18"/>
+      <c r="L31" s="18"/>
+      <c r="M31" s="18"/>
+      <c r="N31" s="18"/>
+      <c r="O31" s="18"/>
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="16"/>
-      <c r="B32" s="15" t="s">
+      <c r="A32" s="17"/>
+      <c r="B32" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
-      <c r="G32" s="13" t="s">
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="H32" s="13"/>
-      <c r="I32" s="13"/>
-      <c r="J32" s="13"/>
-      <c r="K32" s="13"/>
-      <c r="L32" s="13"/>
-      <c r="M32" s="17"/>
-      <c r="N32" s="17"/>
-      <c r="O32" s="17"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="14"/>
+      <c r="K32" s="14"/>
+      <c r="L32" s="14"/>
+      <c r="M32" s="18"/>
+      <c r="N32" s="18"/>
+      <c r="O32" s="18"/>
     </row>
     <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="16"/>
-      <c r="B33" s="12" t="s">
+      <c r="A33" s="17"/>
+      <c r="B33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="17"/>
-      <c r="H33" s="13" t="s">
+      <c r="C33" s="18"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="18"/>
+      <c r="H33" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="I33" s="13"/>
-      <c r="J33" s="13"/>
-      <c r="K33" s="13"/>
-      <c r="L33" s="13"/>
-      <c r="M33" s="17"/>
-      <c r="N33" s="17"/>
-      <c r="O33" s="17"/>
+      <c r="I33" s="14"/>
+      <c r="J33" s="14"/>
+      <c r="K33" s="14"/>
+      <c r="L33" s="14"/>
+      <c r="M33" s="18"/>
+      <c r="N33" s="18"/>
+      <c r="O33" s="18"/>
     </row>
     <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="16"/>
-      <c r="B34" s="10" t="s">
+      <c r="A34" s="17"/>
+      <c r="B34" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="17"/>
-      <c r="G34" s="17"/>
-      <c r="H34" s="17"/>
-      <c r="I34" s="17"/>
-      <c r="J34" s="17"/>
-      <c r="K34" s="17"/>
-      <c r="L34" s="17"/>
-      <c r="M34" s="17"/>
-      <c r="N34" s="17"/>
-      <c r="O34" s="17"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="18"/>
+      <c r="H34" s="18"/>
+      <c r="I34" s="18"/>
+      <c r="J34" s="18"/>
+      <c r="K34" s="18"/>
+      <c r="L34" s="18"/>
+      <c r="M34" s="18"/>
+      <c r="N34" s="18"/>
+      <c r="O34" s="18"/>
     </row>
     <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="16"/>
-      <c r="B35" s="12" t="s">
+      <c r="A35" s="17"/>
+      <c r="B35" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="C35" s="17"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="17"/>
-      <c r="G35" s="17"/>
-      <c r="H35" s="17"/>
-      <c r="I35" s="13" t="s">
+      <c r="C35" s="18"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="18"/>
+      <c r="H35" s="18"/>
+      <c r="I35" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="J35" s="13"/>
-      <c r="K35" s="13"/>
-      <c r="L35" s="13"/>
-      <c r="M35" s="17"/>
-      <c r="N35" s="17"/>
-      <c r="O35" s="17"/>
+      <c r="J35" s="14"/>
+      <c r="K35" s="14"/>
+      <c r="L35" s="14"/>
+      <c r="M35" s="18"/>
+      <c r="N35" s="18"/>
+      <c r="O35" s="18"/>
     </row>
     <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="16"/>
-      <c r="B36" s="12" t="s">
+      <c r="A36" s="17"/>
+      <c r="B36" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="C36" s="17"/>
-      <c r="D36" s="17"/>
-      <c r="E36" s="17"/>
-      <c r="F36" s="17"/>
-      <c r="G36" s="17"/>
-      <c r="H36" s="17"/>
-      <c r="I36" s="13" t="s">
+      <c r="C36" s="18"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="18"/>
+      <c r="H36" s="18"/>
+      <c r="I36" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="J36" s="13"/>
-      <c r="K36" s="13"/>
-      <c r="L36" s="13"/>
-      <c r="M36" s="17"/>
-      <c r="N36" s="17"/>
-      <c r="O36" s="17"/>
+      <c r="J36" s="14"/>
+      <c r="K36" s="14"/>
+      <c r="L36" s="14"/>
+      <c r="M36" s="18"/>
+      <c r="N36" s="18"/>
+      <c r="O36" s="18"/>
     </row>
     <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="16"/>
-      <c r="B37" s="10" t="s">
+      <c r="A37" s="17"/>
+      <c r="B37" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C37" s="17"/>
-      <c r="D37" s="17"/>
-      <c r="E37" s="17"/>
-      <c r="F37" s="17"/>
-      <c r="G37" s="17"/>
-      <c r="H37" s="17"/>
-      <c r="I37" s="17"/>
-      <c r="J37" s="17"/>
-      <c r="K37" s="17"/>
-      <c r="L37" s="17"/>
-      <c r="M37" s="17"/>
-      <c r="N37" s="17"/>
-      <c r="O37" s="17"/>
+      <c r="C37" s="18"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="18"/>
+      <c r="H37" s="18"/>
+      <c r="I37" s="18"/>
+      <c r="J37" s="18"/>
+      <c r="K37" s="18"/>
+      <c r="L37" s="18"/>
+      <c r="M37" s="18"/>
+      <c r="N37" s="18"/>
+      <c r="O37" s="18"/>
     </row>
     <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="16"/>
-      <c r="B38" s="12" t="s">
+      <c r="A38" s="17"/>
+      <c r="B38" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="C38" s="17"/>
-      <c r="D38" s="17"/>
-      <c r="E38" s="17"/>
-      <c r="F38" s="17"/>
-      <c r="G38" s="17"/>
-      <c r="H38" s="17"/>
-      <c r="I38" s="13" t="s">
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="18"/>
+      <c r="H38" s="18"/>
+      <c r="I38" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="J38" s="13"/>
-      <c r="K38" s="13"/>
-      <c r="L38" s="13"/>
-      <c r="M38" s="17"/>
-      <c r="N38" s="17"/>
-      <c r="O38" s="17"/>
+      <c r="J38" s="14"/>
+      <c r="K38" s="14"/>
+      <c r="L38" s="14"/>
+      <c r="M38" s="18"/>
+      <c r="N38" s="18"/>
+      <c r="O38" s="18"/>
     </row>
     <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="16" t="n">
+      <c r="A39" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="B39" s="10" t="s">
+      <c r="B39" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C39" s="20"/>
-      <c r="D39" s="20"/>
-      <c r="E39" s="20"/>
-      <c r="F39" s="20"/>
-      <c r="G39" s="20"/>
-      <c r="H39" s="20"/>
-      <c r="I39" s="20"/>
-      <c r="J39" s="20"/>
-      <c r="K39" s="20"/>
-      <c r="L39" s="20"/>
-      <c r="M39" s="20"/>
-      <c r="N39" s="20"/>
-      <c r="O39" s="20"/>
+      <c r="C39" s="21"/>
+      <c r="D39" s="21"/>
+      <c r="E39" s="21"/>
+      <c r="F39" s="21"/>
+      <c r="G39" s="21"/>
+      <c r="H39" s="21"/>
+      <c r="I39" s="21"/>
+      <c r="J39" s="21"/>
+      <c r="K39" s="21"/>
+      <c r="L39" s="21"/>
+      <c r="M39" s="21"/>
+      <c r="N39" s="21"/>
+      <c r="O39" s="21"/>
     </row>
     <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="16"/>
-      <c r="B40" s="12" t="s">
+      <c r="A40" s="17"/>
+      <c r="B40" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="C40" s="20"/>
-      <c r="D40" s="20"/>
-      <c r="E40" s="20"/>
-      <c r="F40" s="20"/>
-      <c r="G40" s="20"/>
-      <c r="H40" s="20"/>
-      <c r="I40" s="20"/>
-      <c r="J40" s="20"/>
-      <c r="K40" s="20"/>
-      <c r="L40" s="20"/>
-      <c r="M40" s="21" t="s">
+      <c r="C40" s="21"/>
+      <c r="D40" s="21"/>
+      <c r="E40" s="21"/>
+      <c r="F40" s="21"/>
+      <c r="G40" s="21"/>
+      <c r="H40" s="21"/>
+      <c r="I40" s="21"/>
+      <c r="J40" s="21"/>
+      <c r="K40" s="21"/>
+      <c r="L40" s="21"/>
+      <c r="M40" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="N40" s="21"/>
-      <c r="O40" s="21"/>
+      <c r="N40" s="22"/>
+      <c r="O40" s="22"/>
     </row>
     <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="16"/>
-      <c r="B41" s="12" t="s">
+      <c r="A41" s="17"/>
+      <c r="B41" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="C41" s="20"/>
-      <c r="D41" s="20"/>
-      <c r="E41" s="20"/>
-      <c r="F41" s="20"/>
-      <c r="G41" s="20"/>
-      <c r="H41" s="20"/>
-      <c r="I41" s="20"/>
-      <c r="J41" s="20"/>
-      <c r="K41" s="20"/>
-      <c r="L41" s="20"/>
-      <c r="M41" s="21" t="s">
+      <c r="C41" s="21"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="21"/>
+      <c r="F41" s="21"/>
+      <c r="G41" s="21"/>
+      <c r="H41" s="21"/>
+      <c r="I41" s="21"/>
+      <c r="J41" s="21"/>
+      <c r="K41" s="21"/>
+      <c r="L41" s="21"/>
+      <c r="M41" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="N41" s="21"/>
-      <c r="O41" s="21"/>
+      <c r="N41" s="22"/>
+      <c r="O41" s="22"/>
     </row>
     <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="16"/>
-      <c r="B42" s="12" t="s">
+      <c r="A42" s="17"/>
+      <c r="B42" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C42" s="20"/>
-      <c r="D42" s="20"/>
-      <c r="E42" s="20"/>
-      <c r="F42" s="20"/>
-      <c r="G42" s="20"/>
-      <c r="H42" s="20"/>
-      <c r="I42" s="20"/>
-      <c r="J42" s="20"/>
-      <c r="K42" s="20"/>
-      <c r="L42" s="20"/>
-      <c r="M42" s="21" t="s">
+      <c r="C42" s="21"/>
+      <c r="D42" s="21"/>
+      <c r="E42" s="21"/>
+      <c r="F42" s="21"/>
+      <c r="G42" s="21"/>
+      <c r="H42" s="21"/>
+      <c r="I42" s="21"/>
+      <c r="J42" s="21"/>
+      <c r="K42" s="21"/>
+      <c r="L42" s="21"/>
+      <c r="M42" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="N42" s="21"/>
-      <c r="O42" s="21"/>
+      <c r="N42" s="22"/>
+      <c r="O42" s="22"/>
     </row>
     <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="16"/>
-      <c r="B43" s="12" t="s">
+      <c r="A43" s="17"/>
+      <c r="B43" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="C43" s="20"/>
-      <c r="D43" s="20"/>
-      <c r="E43" s="20"/>
-      <c r="F43" s="20"/>
-      <c r="G43" s="20"/>
-      <c r="H43" s="20"/>
-      <c r="I43" s="20"/>
-      <c r="J43" s="20"/>
-      <c r="K43" s="20"/>
-      <c r="L43" s="20"/>
-      <c r="M43" s="21" t="s">
+      <c r="C43" s="21"/>
+      <c r="D43" s="21"/>
+      <c r="E43" s="21"/>
+      <c r="F43" s="21"/>
+      <c r="G43" s="21"/>
+      <c r="H43" s="21"/>
+      <c r="I43" s="21"/>
+      <c r="J43" s="21"/>
+      <c r="K43" s="21"/>
+      <c r="L43" s="21"/>
+      <c r="M43" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="N43" s="21"/>
-      <c r="O43" s="21"/>
+      <c r="N43" s="22"/>
+      <c r="O43" s="22"/>
     </row>
     <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="16"/>
-      <c r="B44" s="12" t="s">
+      <c r="A44" s="17"/>
+      <c r="B44" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="C44" s="20"/>
-      <c r="D44" s="20"/>
-      <c r="E44" s="20"/>
-      <c r="F44" s="20"/>
-      <c r="G44" s="20"/>
-      <c r="H44" s="20"/>
-      <c r="I44" s="20"/>
-      <c r="J44" s="20"/>
-      <c r="K44" s="20"/>
-      <c r="L44" s="20"/>
-      <c r="M44" s="21" t="s">
+      <c r="C44" s="21"/>
+      <c r="D44" s="21"/>
+      <c r="E44" s="21"/>
+      <c r="F44" s="21"/>
+      <c r="G44" s="21"/>
+      <c r="H44" s="21"/>
+      <c r="I44" s="21"/>
+      <c r="J44" s="21"/>
+      <c r="K44" s="21"/>
+      <c r="L44" s="21"/>
+      <c r="M44" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="N44" s="21"/>
-      <c r="O44" s="21"/>
+      <c r="N44" s="22"/>
+      <c r="O44" s="22"/>
     </row>
     <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="16"/>
-      <c r="B45" s="10" t="s">
+      <c r="A45" s="17"/>
+      <c r="B45" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="C45" s="20"/>
-      <c r="D45" s="20"/>
-      <c r="E45" s="20"/>
-      <c r="F45" s="20"/>
-      <c r="G45" s="20"/>
-      <c r="H45" s="20"/>
-      <c r="I45" s="20"/>
-      <c r="J45" s="20"/>
-      <c r="K45" s="20"/>
-      <c r="L45" s="20"/>
-      <c r="M45" s="20"/>
-      <c r="N45" s="20"/>
-      <c r="O45" s="20"/>
+      <c r="C45" s="21"/>
+      <c r="D45" s="21"/>
+      <c r="E45" s="21"/>
+      <c r="F45" s="21"/>
+      <c r="G45" s="21"/>
+      <c r="H45" s="21"/>
+      <c r="I45" s="21"/>
+      <c r="J45" s="21"/>
+      <c r="K45" s="21"/>
+      <c r="L45" s="21"/>
+      <c r="M45" s="21"/>
+      <c r="N45" s="21"/>
+      <c r="O45" s="21"/>
     </row>
     <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="16"/>
-      <c r="B46" s="12" t="s">
+      <c r="A46" s="17"/>
+      <c r="B46" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="C46" s="20"/>
-      <c r="D46" s="20"/>
-      <c r="E46" s="20"/>
-      <c r="F46" s="20"/>
-      <c r="G46" s="20"/>
-      <c r="H46" s="20"/>
-      <c r="I46" s="20"/>
-      <c r="J46" s="20"/>
-      <c r="K46" s="20"/>
-      <c r="L46" s="20"/>
-      <c r="M46" s="21" t="s">
+      <c r="C46" s="21"/>
+      <c r="D46" s="21"/>
+      <c r="E46" s="21"/>
+      <c r="F46" s="21"/>
+      <c r="G46" s="21"/>
+      <c r="H46" s="21"/>
+      <c r="I46" s="21"/>
+      <c r="J46" s="21"/>
+      <c r="K46" s="21"/>
+      <c r="L46" s="21"/>
+      <c r="M46" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="N46" s="21"/>
-      <c r="O46" s="21"/>
+      <c r="N46" s="22"/>
+      <c r="O46" s="22"/>
     </row>
     <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="16"/>
-      <c r="B47" s="10" t="s">
+      <c r="A47" s="17"/>
+      <c r="B47" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="C47" s="20"/>
-      <c r="D47" s="20"/>
-      <c r="E47" s="20"/>
-      <c r="F47" s="20"/>
-      <c r="G47" s="20"/>
-      <c r="H47" s="20"/>
-      <c r="I47" s="20"/>
-      <c r="J47" s="20"/>
-      <c r="K47" s="20"/>
-      <c r="L47" s="20"/>
-      <c r="M47" s="20"/>
-      <c r="N47" s="20"/>
-      <c r="O47" s="20"/>
+      <c r="C47" s="21"/>
+      <c r="D47" s="21"/>
+      <c r="E47" s="21"/>
+      <c r="F47" s="21"/>
+      <c r="G47" s="21"/>
+      <c r="H47" s="21"/>
+      <c r="I47" s="21"/>
+      <c r="J47" s="21"/>
+      <c r="K47" s="21"/>
+      <c r="L47" s="21"/>
+      <c r="M47" s="21"/>
+      <c r="N47" s="21"/>
+      <c r="O47" s="21"/>
     </row>
     <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="16"/>
-      <c r="B48" s="12" t="s">
+      <c r="A48" s="17"/>
+      <c r="B48" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="C48" s="20"/>
-      <c r="D48" s="20"/>
-      <c r="E48" s="13" t="s">
+      <c r="C48" s="21"/>
+      <c r="D48" s="21"/>
+      <c r="E48" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="F48" s="13"/>
-      <c r="G48" s="13"/>
-      <c r="H48" s="13"/>
-      <c r="I48" s="13"/>
-      <c r="J48" s="13"/>
-      <c r="K48" s="13"/>
-      <c r="L48" s="13"/>
-      <c r="M48" s="13"/>
-      <c r="N48" s="13"/>
-      <c r="O48" s="13"/>
+      <c r="F48" s="14"/>
+      <c r="G48" s="14"/>
+      <c r="H48" s="14"/>
+      <c r="I48" s="14"/>
+      <c r="J48" s="14"/>
+      <c r="K48" s="14"/>
+      <c r="L48" s="14"/>
+      <c r="M48" s="14"/>
+      <c r="N48" s="14"/>
+      <c r="O48" s="14"/>
     </row>
     <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="16"/>
-      <c r="B49" s="10" t="s">
+      <c r="A49" s="17"/>
+      <c r="B49" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="C49" s="20"/>
-      <c r="D49" s="20"/>
-      <c r="E49" s="20"/>
-      <c r="F49" s="20"/>
-      <c r="G49" s="20"/>
-      <c r="H49" s="20"/>
-      <c r="I49" s="20"/>
-      <c r="J49" s="20"/>
-      <c r="K49" s="13" t="s">
+      <c r="C49" s="21"/>
+      <c r="D49" s="21"/>
+      <c r="E49" s="21"/>
+      <c r="F49" s="21"/>
+      <c r="G49" s="21"/>
+      <c r="H49" s="21"/>
+      <c r="I49" s="21"/>
+      <c r="J49" s="21"/>
+      <c r="K49" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="L49" s="13"/>
-      <c r="M49" s="13"/>
-      <c r="N49" s="13"/>
-      <c r="O49" s="13"/>
+      <c r="L49" s="14"/>
+      <c r="M49" s="14"/>
+      <c r="N49" s="14"/>
+      <c r="O49" s="14"/>
     </row>
     <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="16"/>
-      <c r="B50" s="10" t="s">
+      <c r="A50" s="17"/>
+      <c r="B50" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="C50" s="20"/>
-      <c r="D50" s="20"/>
-      <c r="E50" s="13" t="s">
+      <c r="C50" s="21"/>
+      <c r="D50" s="21"/>
+      <c r="E50" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="F50" s="13"/>
-      <c r="G50" s="13"/>
-      <c r="H50" s="13"/>
-      <c r="I50" s="13"/>
-      <c r="J50" s="13"/>
-      <c r="K50" s="13"/>
-      <c r="L50" s="13"/>
-      <c r="M50" s="13"/>
-      <c r="N50" s="13"/>
-      <c r="O50" s="13"/>
+      <c r="F50" s="14"/>
+      <c r="G50" s="14"/>
+      <c r="H50" s="14"/>
+      <c r="I50" s="14"/>
+      <c r="J50" s="14"/>
+      <c r="K50" s="14"/>
+      <c r="L50" s="14"/>
+      <c r="M50" s="14"/>
+      <c r="N50" s="14"/>
+      <c r="O50" s="14"/>
     </row>
     <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="16"/>
-      <c r="B51" s="10" t="s">
+      <c r="A51" s="17"/>
+      <c r="B51" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="C51" s="20"/>
-      <c r="D51" s="20"/>
-      <c r="E51" s="20"/>
-      <c r="F51" s="20"/>
-      <c r="G51" s="20"/>
-      <c r="H51" s="20"/>
-      <c r="I51" s="20"/>
-      <c r="J51" s="20"/>
-      <c r="K51" s="20"/>
-      <c r="L51" s="13" t="s">
+      <c r="C51" s="21"/>
+      <c r="D51" s="21"/>
+      <c r="E51" s="21"/>
+      <c r="F51" s="21"/>
+      <c r="G51" s="21"/>
+      <c r="H51" s="21"/>
+      <c r="I51" s="21"/>
+      <c r="J51" s="21"/>
+      <c r="K51" s="21"/>
+      <c r="L51" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="M51" s="13"/>
-      <c r="N51" s="13"/>
-      <c r="O51" s="13"/>
+      <c r="M51" s="14"/>
+      <c r="N51" s="14"/>
+      <c r="O51" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="34">

--- a/docs/Project Plan.xlsx
+++ b/docs/Project Plan.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="60">
   <si>
     <t xml:space="preserve">Phase</t>
   </si>
@@ -46,10 +46,10 @@
     <t xml:space="preserve">2. Set up Raspberry Pi as Server and confirmed communication</t>
   </si>
   <si>
+    <t xml:space="preserve">     Set up Raspberry Pi as a server </t>
+  </si>
+  <si>
     <t xml:space="preserve">Fergus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     Set up Raspberry Pi as a server </t>
   </si>
   <si>
     <t xml:space="preserve">     Confirm communication between client computer and server (HTTP/SSH) </t>
@@ -74,6 +74,9 @@
      request, door open/close, location of elevator car</t>
   </si>
   <si>
+    <t xml:space="preserve">Ryan</t>
+  </si>
+  <si>
     <t xml:space="preserve">    Develop and implement a test plan to confirm functionality of software/hardware</t>
   </si>
   <si>
@@ -83,7 +86,7 @@
     <t xml:space="preserve">     Controls (up/down) built in HTML (possibly add CSS if students work ahead)</t>
   </si>
   <si>
-    <t xml:space="preserve">Ryan</t>
+    <t xml:space="preserve">Fergus/Ryan</t>
   </si>
   <si>
     <t xml:space="preserve">     Elevator Car Controls (up/down/floor number) built in HTML (possibly CSS if students work ahead)</t>
@@ -102,9 +105,6 @@
   </si>
   <si>
     <t xml:space="preserve">    User action buttons/icons implemented</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fergus/Ryan</t>
   </si>
   <si>
     <t xml:space="preserve">    Indicators/lights etc. implemented</t>
@@ -210,7 +210,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -279,8 +279,15 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <i val="true"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="DejaVu Sans"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -326,17 +333,23 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.05"/>
-        <bgColor rgb="FFEDEDED"/>
+        <bgColor rgb="FFEEEEEE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.7999"/>
-        <bgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FFEEEEEE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEEEEE"/>
+        <bgColor rgb="FFEDEDED"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -358,13 +371,6 @@
       <bottom style="hair"/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right style="hair"/>
-      <top style="hair"/>
-      <bottom style="hair"/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -391,7 +397,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -460,6 +466,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="10" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -468,11 +478,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -528,9 +538,9 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFEEEEEE"/>
+      <rgbColor rgb="FFE2F0D9"/>
       <rgbColor rgb="FFF2F2F2"/>
-      <rgbColor rgb="FFE2F0D9"/>
-      <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
@@ -859,9 +869,7 @@
       <c r="B5" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="15" t="s">
-        <v>8</v>
-      </c>
+      <c r="C5" s="12"/>
       <c r="D5" s="12"/>
       <c r="E5" s="12"/>
       <c r="F5" s="12"/>
@@ -878,10 +886,10 @@
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="10"/>
       <c r="B6" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="15" t="s">
         <v>9</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>8</v>
       </c>
       <c r="D6" s="12"/>
       <c r="E6" s="12"/>
@@ -902,10 +910,10 @@
         <v>10</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
+        <v>9</v>
+      </c>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
       <c r="F7" s="12"/>
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
@@ -944,7 +952,7 @@
       <c r="C9" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="12"/>
+      <c r="D9" s="15"/>
       <c r="E9" s="12"/>
       <c r="F9" s="12"/>
       <c r="G9" s="12"/>
@@ -1006,9 +1014,9 @@
       </c>
       <c r="C12" s="12"/>
       <c r="D12" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" s="12"/>
+        <v>17</v>
+      </c>
+      <c r="E12" s="15"/>
       <c r="F12" s="12"/>
       <c r="G12" s="12"/>
       <c r="H12" s="12"/>
@@ -1023,13 +1031,13 @@
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="10"/>
       <c r="B13" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="12"/>
-      <c r="D13" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" s="12"/>
+        <v>18</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
       <c r="F13" s="12"/>
       <c r="G13" s="12"/>
       <c r="H13" s="12"/>
@@ -1044,7 +1052,7 @@
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="10"/>
       <c r="B14" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C14" s="12"/>
       <c r="D14" s="12"/>
@@ -1063,10 +1071,10 @@
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="10"/>
       <c r="B15" s="13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D15" s="15"/>
       <c r="E15" s="15"/>
@@ -1084,13 +1092,13 @@
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="10"/>
       <c r="B16" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="12"/>
-      <c r="D16" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="12"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
       <c r="F16" s="12"/>
       <c r="G16" s="12"/>
       <c r="H16" s="12"/>
@@ -1105,7 +1113,7 @@
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="10"/>
       <c r="B17" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -1124,10 +1132,10 @@
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="10"/>
       <c r="B18" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D18" s="15"/>
       <c r="E18" s="15"/>
@@ -1143,220 +1151,220 @@
       <c r="O18" s="12"/>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="17" t="n">
+      <c r="A19" s="18" t="n">
         <v>2</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="18"/>
-      <c r="I19" s="18"/>
-      <c r="J19" s="18"/>
-      <c r="K19" s="18"/>
-      <c r="L19" s="18"/>
-      <c r="M19" s="18"/>
-      <c r="N19" s="18"/>
-      <c r="O19" s="18"/>
+        <v>25</v>
+      </c>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="19"/>
+      <c r="J19" s="19"/>
+      <c r="K19" s="19"/>
+      <c r="L19" s="19"/>
+      <c r="M19" s="19"/>
+      <c r="N19" s="19"/>
+      <c r="O19" s="19"/>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="17"/>
+      <c r="A20" s="18"/>
       <c r="B20" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="18"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="G20" s="19"/>
-      <c r="H20" s="19"/>
-      <c r="I20" s="19"/>
-      <c r="J20" s="19"/>
-      <c r="K20" s="19"/>
-      <c r="L20" s="19"/>
-      <c r="M20" s="19"/>
-      <c r="N20" s="18"/>
-      <c r="O20" s="18"/>
+        <v>26</v>
+      </c>
+      <c r="C20" s="19"/>
+      <c r="D20" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20" s="17"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="17"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="17"/>
+      <c r="L20" s="17"/>
+      <c r="M20" s="17"/>
+      <c r="N20" s="19"/>
+      <c r="O20" s="19"/>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="17"/>
+      <c r="A21" s="18"/>
       <c r="B21" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21" s="18"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="18"/>
-      <c r="J21" s="18"/>
-      <c r="K21" s="18"/>
-      <c r="L21" s="18"/>
-      <c r="M21" s="18"/>
-      <c r="N21" s="18"/>
-      <c r="O21" s="18"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="19"/>
+      <c r="J21" s="19"/>
+      <c r="K21" s="19"/>
+      <c r="L21" s="19"/>
+      <c r="M21" s="19"/>
+      <c r="N21" s="19"/>
+      <c r="O21" s="19"/>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="17"/>
+      <c r="A22" s="18"/>
       <c r="B22" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C22" s="18"/>
-      <c r="D22" s="18"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
       <c r="E22" s="14" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F22" s="14"/>
       <c r="G22" s="14"/>
       <c r="H22" s="14"/>
-      <c r="I22" s="18"/>
-      <c r="J22" s="18"/>
-      <c r="K22" s="18"/>
-      <c r="L22" s="18"/>
-      <c r="M22" s="18"/>
-      <c r="N22" s="18"/>
-      <c r="O22" s="18"/>
+      <c r="I22" s="19"/>
+      <c r="J22" s="19"/>
+      <c r="K22" s="19"/>
+      <c r="L22" s="19"/>
+      <c r="M22" s="19"/>
+      <c r="N22" s="19"/>
+      <c r="O22" s="19"/>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="17"/>
+      <c r="A23" s="18"/>
       <c r="B23" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="I23" s="14"/>
-      <c r="J23" s="14"/>
-      <c r="K23" s="18"/>
-      <c r="L23" s="18"/>
-      <c r="M23" s="18"/>
-      <c r="N23" s="18"/>
-      <c r="O23" s="18"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="19"/>
+      <c r="K23" s="19"/>
+      <c r="L23" s="19"/>
+      <c r="M23" s="19"/>
+      <c r="N23" s="19"/>
+      <c r="O23" s="19"/>
       <c r="Q23" s="20"/>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="17"/>
+      <c r="A24" s="18"/>
       <c r="B24" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="19"/>
       <c r="H24" s="14" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="18"/>
-      <c r="L24" s="18"/>
-      <c r="M24" s="18"/>
-      <c r="N24" s="18"/>
-      <c r="O24" s="18"/>
+      <c r="K24" s="19"/>
+      <c r="L24" s="19"/>
+      <c r="M24" s="19"/>
+      <c r="N24" s="19"/>
+      <c r="O24" s="19"/>
       <c r="Q24" s="20"/>
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="17"/>
+      <c r="A25" s="18"/>
       <c r="B25" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="18"/>
-      <c r="H25" s="18"/>
-      <c r="I25" s="18"/>
-      <c r="J25" s="18"/>
-      <c r="K25" s="18"/>
-      <c r="L25" s="18"/>
-      <c r="M25" s="18"/>
-      <c r="N25" s="18"/>
-      <c r="O25" s="18"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="19"/>
+      <c r="M25" s="19"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="19"/>
     </row>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="17"/>
+      <c r="A26" s="18"/>
       <c r="B26" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
       <c r="H26" s="14" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I26" s="14"/>
       <c r="J26" s="14"/>
-      <c r="K26" s="18"/>
-      <c r="L26" s="18"/>
-      <c r="M26" s="18"/>
-      <c r="N26" s="18"/>
-      <c r="O26" s="18"/>
+      <c r="K26" s="19"/>
+      <c r="L26" s="19"/>
+      <c r="M26" s="19"/>
+      <c r="N26" s="19"/>
+      <c r="O26" s="19"/>
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="17"/>
+      <c r="A27" s="18"/>
       <c r="B27" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="18"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
       <c r="H27" s="14" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I27" s="14"/>
       <c r="J27" s="14"/>
-      <c r="K27" s="18"/>
-      <c r="L27" s="18"/>
-      <c r="M27" s="18"/>
-      <c r="N27" s="18"/>
-      <c r="O27" s="18"/>
+      <c r="K27" s="19"/>
+      <c r="L27" s="19"/>
+      <c r="M27" s="19"/>
+      <c r="N27" s="19"/>
+      <c r="O27" s="19"/>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="17"/>
+      <c r="A28" s="18"/>
       <c r="B28" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="18"/>
-      <c r="H28" s="18"/>
-      <c r="I28" s="18"/>
-      <c r="J28" s="18"/>
-      <c r="K28" s="18"/>
-      <c r="L28" s="18"/>
-      <c r="M28" s="18"/>
-      <c r="N28" s="18"/>
-      <c r="O28" s="18"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19"/>
+      <c r="K28" s="19"/>
+      <c r="L28" s="19"/>
+      <c r="M28" s="19"/>
+      <c r="N28" s="19"/>
+      <c r="O28" s="19"/>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="17"/>
+      <c r="A29" s="18"/>
       <c r="B29" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
       <c r="E29" s="14" t="s">
         <v>36</v>
       </c>
@@ -1366,18 +1374,18 @@
       <c r="I29" s="14"/>
       <c r="J29" s="14"/>
       <c r="K29" s="14"/>
-      <c r="L29" s="18"/>
-      <c r="M29" s="18"/>
-      <c r="N29" s="18"/>
-      <c r="O29" s="18"/>
+      <c r="L29" s="19"/>
+      <c r="M29" s="19"/>
+      <c r="N29" s="19"/>
+      <c r="O29" s="19"/>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="17"/>
-      <c r="B30" s="13" t="s">
+      <c r="A30" s="18"/>
+      <c r="B30" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
       <c r="E30" s="14" t="s">
         <v>13</v>
       </c>
@@ -1388,364 +1396,364 @@
       <c r="J30" s="14"/>
       <c r="K30" s="14"/>
       <c r="L30" s="14"/>
-      <c r="M30" s="18"/>
-      <c r="N30" s="18"/>
-      <c r="O30" s="18"/>
+      <c r="M30" s="19"/>
+      <c r="N30" s="19"/>
+      <c r="O30" s="19"/>
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="17"/>
+      <c r="A31" s="18"/>
       <c r="B31" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="18"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="18"/>
-      <c r="H31" s="18"/>
-      <c r="I31" s="18"/>
-      <c r="J31" s="18"/>
-      <c r="K31" s="18"/>
-      <c r="L31" s="18"/>
-      <c r="M31" s="18"/>
-      <c r="N31" s="18"/>
-      <c r="O31" s="18"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="19"/>
+      <c r="I31" s="19"/>
+      <c r="J31" s="19"/>
+      <c r="K31" s="19"/>
+      <c r="L31" s="19"/>
+      <c r="M31" s="19"/>
+      <c r="N31" s="19"/>
+      <c r="O31" s="19"/>
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="17"/>
+      <c r="A32" s="18"/>
       <c r="B32" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
       <c r="G32" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H32" s="14"/>
       <c r="I32" s="14"/>
       <c r="J32" s="14"/>
       <c r="K32" s="14"/>
       <c r="L32" s="14"/>
-      <c r="M32" s="18"/>
-      <c r="N32" s="18"/>
-      <c r="O32" s="18"/>
+      <c r="M32" s="19"/>
+      <c r="N32" s="19"/>
+      <c r="O32" s="19"/>
     </row>
     <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="17"/>
+      <c r="A33" s="18"/>
       <c r="B33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="18"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="18"/>
-      <c r="G33" s="18"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="19"/>
       <c r="H33" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I33" s="14"/>
       <c r="J33" s="14"/>
       <c r="K33" s="14"/>
       <c r="L33" s="14"/>
-      <c r="M33" s="18"/>
-      <c r="N33" s="18"/>
-      <c r="O33" s="18"/>
+      <c r="M33" s="19"/>
+      <c r="N33" s="19"/>
+      <c r="O33" s="19"/>
     </row>
     <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="17"/>
+      <c r="A34" s="18"/>
       <c r="B34" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="18"/>
-      <c r="H34" s="18"/>
-      <c r="I34" s="18"/>
-      <c r="J34" s="18"/>
-      <c r="K34" s="18"/>
-      <c r="L34" s="18"/>
-      <c r="M34" s="18"/>
-      <c r="N34" s="18"/>
-      <c r="O34" s="18"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="19"/>
+      <c r="I34" s="19"/>
+      <c r="J34" s="19"/>
+      <c r="K34" s="19"/>
+      <c r="L34" s="19"/>
+      <c r="M34" s="19"/>
+      <c r="N34" s="19"/>
+      <c r="O34" s="19"/>
     </row>
     <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="17"/>
+      <c r="A35" s="18"/>
       <c r="B35" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="C35" s="18"/>
-      <c r="D35" s="18"/>
-      <c r="E35" s="18"/>
-      <c r="F35" s="18"/>
-      <c r="G35" s="18"/>
-      <c r="H35" s="18"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="19"/>
+      <c r="F35" s="19"/>
+      <c r="G35" s="19"/>
+      <c r="H35" s="19"/>
       <c r="I35" s="14" t="s">
         <v>13</v>
       </c>
       <c r="J35" s="14"/>
       <c r="K35" s="14"/>
       <c r="L35" s="14"/>
-      <c r="M35" s="18"/>
-      <c r="N35" s="18"/>
-      <c r="O35" s="18"/>
+      <c r="M35" s="19"/>
+      <c r="N35" s="19"/>
+      <c r="O35" s="19"/>
     </row>
     <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="17"/>
+      <c r="A36" s="18"/>
       <c r="B36" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="C36" s="18"/>
-      <c r="D36" s="18"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="18"/>
-      <c r="G36" s="18"/>
-      <c r="H36" s="18"/>
+      <c r="C36" s="19"/>
+      <c r="D36" s="19"/>
+      <c r="E36" s="19"/>
+      <c r="F36" s="19"/>
+      <c r="G36" s="19"/>
+      <c r="H36" s="19"/>
       <c r="I36" s="14" t="s">
         <v>13</v>
       </c>
       <c r="J36" s="14"/>
       <c r="K36" s="14"/>
       <c r="L36" s="14"/>
-      <c r="M36" s="18"/>
-      <c r="N36" s="18"/>
-      <c r="O36" s="18"/>
+      <c r="M36" s="19"/>
+      <c r="N36" s="19"/>
+      <c r="O36" s="19"/>
     </row>
     <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="17"/>
+      <c r="A37" s="18"/>
       <c r="B37" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C37" s="18"/>
-      <c r="D37" s="18"/>
-      <c r="E37" s="18"/>
-      <c r="F37" s="18"/>
-      <c r="G37" s="18"/>
-      <c r="H37" s="18"/>
-      <c r="I37" s="18"/>
-      <c r="J37" s="18"/>
-      <c r="K37" s="18"/>
-      <c r="L37" s="18"/>
-      <c r="M37" s="18"/>
-      <c r="N37" s="18"/>
-      <c r="O37" s="18"/>
+      <c r="C37" s="19"/>
+      <c r="D37" s="19"/>
+      <c r="E37" s="19"/>
+      <c r="F37" s="19"/>
+      <c r="G37" s="19"/>
+      <c r="H37" s="19"/>
+      <c r="I37" s="19"/>
+      <c r="J37" s="19"/>
+      <c r="K37" s="19"/>
+      <c r="L37" s="19"/>
+      <c r="M37" s="19"/>
+      <c r="N37" s="19"/>
+      <c r="O37" s="19"/>
     </row>
     <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="17"/>
+      <c r="A38" s="18"/>
       <c r="B38" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="C38" s="18"/>
-      <c r="D38" s="18"/>
-      <c r="E38" s="18"/>
-      <c r="F38" s="18"/>
-      <c r="G38" s="18"/>
-      <c r="H38" s="18"/>
+      <c r="C38" s="19"/>
+      <c r="D38" s="19"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="19"/>
+      <c r="G38" s="19"/>
+      <c r="H38" s="19"/>
       <c r="I38" s="14" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J38" s="14"/>
       <c r="K38" s="14"/>
       <c r="L38" s="14"/>
-      <c r="M38" s="18"/>
-      <c r="N38" s="18"/>
-      <c r="O38" s="18"/>
+      <c r="M38" s="19"/>
+      <c r="N38" s="19"/>
+      <c r="O38" s="19"/>
     </row>
     <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="17" t="n">
+      <c r="A39" s="18" t="n">
         <v>3</v>
       </c>
       <c r="B39" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C39" s="21"/>
-      <c r="D39" s="21"/>
-      <c r="E39" s="21"/>
-      <c r="F39" s="21"/>
-      <c r="G39" s="21"/>
-      <c r="H39" s="21"/>
-      <c r="I39" s="21"/>
-      <c r="J39" s="21"/>
-      <c r="K39" s="21"/>
-      <c r="L39" s="21"/>
-      <c r="M39" s="21"/>
-      <c r="N39" s="21"/>
-      <c r="O39" s="21"/>
+      <c r="C39" s="22"/>
+      <c r="D39" s="22"/>
+      <c r="E39" s="22"/>
+      <c r="F39" s="22"/>
+      <c r="G39" s="22"/>
+      <c r="H39" s="22"/>
+      <c r="I39" s="22"/>
+      <c r="J39" s="22"/>
+      <c r="K39" s="22"/>
+      <c r="L39" s="22"/>
+      <c r="M39" s="22"/>
+      <c r="N39" s="22"/>
+      <c r="O39" s="22"/>
     </row>
     <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="17"/>
+      <c r="A40" s="18"/>
       <c r="B40" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="C40" s="21"/>
-      <c r="D40" s="21"/>
-      <c r="E40" s="21"/>
-      <c r="F40" s="21"/>
-      <c r="G40" s="21"/>
-      <c r="H40" s="21"/>
-      <c r="I40" s="21"/>
-      <c r="J40" s="21"/>
-      <c r="K40" s="21"/>
-      <c r="L40" s="21"/>
-      <c r="M40" s="22" t="s">
+      <c r="C40" s="22"/>
+      <c r="D40" s="22"/>
+      <c r="E40" s="22"/>
+      <c r="F40" s="22"/>
+      <c r="G40" s="22"/>
+      <c r="H40" s="22"/>
+      <c r="I40" s="22"/>
+      <c r="J40" s="22"/>
+      <c r="K40" s="22"/>
+      <c r="L40" s="22"/>
+      <c r="M40" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N40" s="22"/>
-      <c r="O40" s="22"/>
+      <c r="N40" s="23"/>
+      <c r="O40" s="23"/>
     </row>
     <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="17"/>
+      <c r="A41" s="18"/>
       <c r="B41" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="C41" s="21"/>
-      <c r="D41" s="21"/>
-      <c r="E41" s="21"/>
-      <c r="F41" s="21"/>
-      <c r="G41" s="21"/>
-      <c r="H41" s="21"/>
-      <c r="I41" s="21"/>
-      <c r="J41" s="21"/>
-      <c r="K41" s="21"/>
-      <c r="L41" s="21"/>
-      <c r="M41" s="22" t="s">
+      <c r="C41" s="22"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="22"/>
+      <c r="F41" s="22"/>
+      <c r="G41" s="22"/>
+      <c r="H41" s="22"/>
+      <c r="I41" s="22"/>
+      <c r="J41" s="22"/>
+      <c r="K41" s="22"/>
+      <c r="L41" s="22"/>
+      <c r="M41" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N41" s="22"/>
-      <c r="O41" s="22"/>
+      <c r="N41" s="23"/>
+      <c r="O41" s="23"/>
     </row>
     <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="17"/>
+      <c r="A42" s="18"/>
       <c r="B42" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C42" s="21"/>
-      <c r="D42" s="21"/>
-      <c r="E42" s="21"/>
-      <c r="F42" s="21"/>
-      <c r="G42" s="21"/>
-      <c r="H42" s="21"/>
-      <c r="I42" s="21"/>
-      <c r="J42" s="21"/>
-      <c r="K42" s="21"/>
-      <c r="L42" s="21"/>
-      <c r="M42" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="N42" s="22"/>
-      <c r="O42" s="22"/>
+      <c r="C42" s="22"/>
+      <c r="D42" s="22"/>
+      <c r="E42" s="22"/>
+      <c r="F42" s="22"/>
+      <c r="G42" s="22"/>
+      <c r="H42" s="22"/>
+      <c r="I42" s="22"/>
+      <c r="J42" s="22"/>
+      <c r="K42" s="22"/>
+      <c r="L42" s="22"/>
+      <c r="M42" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="N42" s="23"/>
+      <c r="O42" s="23"/>
     </row>
     <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="17"/>
+      <c r="A43" s="18"/>
       <c r="B43" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="C43" s="21"/>
-      <c r="D43" s="21"/>
-      <c r="E43" s="21"/>
-      <c r="F43" s="21"/>
-      <c r="G43" s="21"/>
-      <c r="H43" s="21"/>
-      <c r="I43" s="21"/>
-      <c r="J43" s="21"/>
-      <c r="K43" s="21"/>
-      <c r="L43" s="21"/>
-      <c r="M43" s="22" t="s">
+      <c r="C43" s="22"/>
+      <c r="D43" s="22"/>
+      <c r="E43" s="22"/>
+      <c r="F43" s="22"/>
+      <c r="G43" s="22"/>
+      <c r="H43" s="22"/>
+      <c r="I43" s="22"/>
+      <c r="J43" s="22"/>
+      <c r="K43" s="22"/>
+      <c r="L43" s="22"/>
+      <c r="M43" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="N43" s="22"/>
-      <c r="O43" s="22"/>
+      <c r="N43" s="23"/>
+      <c r="O43" s="23"/>
     </row>
     <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="17"/>
+      <c r="A44" s="18"/>
       <c r="B44" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="C44" s="21"/>
-      <c r="D44" s="21"/>
-      <c r="E44" s="21"/>
-      <c r="F44" s="21"/>
-      <c r="G44" s="21"/>
-      <c r="H44" s="21"/>
-      <c r="I44" s="21"/>
-      <c r="J44" s="21"/>
-      <c r="K44" s="21"/>
-      <c r="L44" s="21"/>
-      <c r="M44" s="22" t="s">
+      <c r="C44" s="22"/>
+      <c r="D44" s="22"/>
+      <c r="E44" s="22"/>
+      <c r="F44" s="22"/>
+      <c r="G44" s="22"/>
+      <c r="H44" s="22"/>
+      <c r="I44" s="22"/>
+      <c r="J44" s="22"/>
+      <c r="K44" s="22"/>
+      <c r="L44" s="22"/>
+      <c r="M44" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="N44" s="22"/>
-      <c r="O44" s="22"/>
+      <c r="N44" s="23"/>
+      <c r="O44" s="23"/>
     </row>
     <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="17"/>
+      <c r="A45" s="18"/>
       <c r="B45" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="C45" s="21"/>
-      <c r="D45" s="21"/>
-      <c r="E45" s="21"/>
-      <c r="F45" s="21"/>
-      <c r="G45" s="21"/>
-      <c r="H45" s="21"/>
-      <c r="I45" s="21"/>
-      <c r="J45" s="21"/>
-      <c r="K45" s="21"/>
-      <c r="L45" s="21"/>
-      <c r="M45" s="21"/>
-      <c r="N45" s="21"/>
-      <c r="O45" s="21"/>
+      <c r="C45" s="22"/>
+      <c r="D45" s="22"/>
+      <c r="E45" s="22"/>
+      <c r="F45" s="22"/>
+      <c r="G45" s="22"/>
+      <c r="H45" s="22"/>
+      <c r="I45" s="22"/>
+      <c r="J45" s="22"/>
+      <c r="K45" s="22"/>
+      <c r="L45" s="22"/>
+      <c r="M45" s="22"/>
+      <c r="N45" s="22"/>
+      <c r="O45" s="22"/>
     </row>
     <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="17"/>
+      <c r="A46" s="18"/>
       <c r="B46" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="C46" s="21"/>
-      <c r="D46" s="21"/>
-      <c r="E46" s="21"/>
-      <c r="F46" s="21"/>
-      <c r="G46" s="21"/>
-      <c r="H46" s="21"/>
-      <c r="I46" s="21"/>
-      <c r="J46" s="21"/>
-      <c r="K46" s="21"/>
-      <c r="L46" s="21"/>
-      <c r="M46" s="22" t="s">
+      <c r="C46" s="22"/>
+      <c r="D46" s="22"/>
+      <c r="E46" s="22"/>
+      <c r="F46" s="22"/>
+      <c r="G46" s="22"/>
+      <c r="H46" s="22"/>
+      <c r="I46" s="22"/>
+      <c r="J46" s="22"/>
+      <c r="K46" s="22"/>
+      <c r="L46" s="22"/>
+      <c r="M46" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="N46" s="22"/>
-      <c r="O46" s="22"/>
+      <c r="N46" s="23"/>
+      <c r="O46" s="23"/>
     </row>
     <row r="47" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="17"/>
+      <c r="A47" s="18"/>
       <c r="B47" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="C47" s="21"/>
-      <c r="D47" s="21"/>
-      <c r="E47" s="21"/>
-      <c r="F47" s="21"/>
-      <c r="G47" s="21"/>
-      <c r="H47" s="21"/>
-      <c r="I47" s="21"/>
-      <c r="J47" s="21"/>
-      <c r="K47" s="21"/>
-      <c r="L47" s="21"/>
-      <c r="M47" s="21"/>
-      <c r="N47" s="21"/>
-      <c r="O47" s="21"/>
+      <c r="C47" s="22"/>
+      <c r="D47" s="22"/>
+      <c r="E47" s="22"/>
+      <c r="F47" s="22"/>
+      <c r="G47" s="22"/>
+      <c r="H47" s="22"/>
+      <c r="I47" s="22"/>
+      <c r="J47" s="22"/>
+      <c r="K47" s="22"/>
+      <c r="L47" s="22"/>
+      <c r="M47" s="22"/>
+      <c r="N47" s="22"/>
+      <c r="O47" s="22"/>
     </row>
     <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="17"/>
+      <c r="A48" s="18"/>
       <c r="B48" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="C48" s="21"/>
-      <c r="D48" s="21"/>
+      <c r="C48" s="22"/>
+      <c r="D48" s="22"/>
       <c r="E48" s="14" t="s">
         <v>13</v>
       </c>
@@ -1761,18 +1769,18 @@
       <c r="O48" s="14"/>
     </row>
     <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="17"/>
+      <c r="A49" s="18"/>
       <c r="B49" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="C49" s="21"/>
-      <c r="D49" s="21"/>
-      <c r="E49" s="21"/>
-      <c r="F49" s="21"/>
-      <c r="G49" s="21"/>
-      <c r="H49" s="21"/>
-      <c r="I49" s="21"/>
-      <c r="J49" s="21"/>
+      <c r="C49" s="22"/>
+      <c r="D49" s="22"/>
+      <c r="E49" s="22"/>
+      <c r="F49" s="22"/>
+      <c r="G49" s="22"/>
+      <c r="H49" s="22"/>
+      <c r="I49" s="22"/>
+      <c r="J49" s="22"/>
       <c r="K49" s="14" t="s">
         <v>13</v>
       </c>
@@ -1782,12 +1790,12 @@
       <c r="O49" s="14"/>
     </row>
     <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="17"/>
+      <c r="A50" s="18"/>
       <c r="B50" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="C50" s="21"/>
-      <c r="D50" s="21"/>
+      <c r="C50" s="22"/>
+      <c r="D50" s="22"/>
       <c r="E50" s="14" t="s">
         <v>6</v>
       </c>
@@ -1803,19 +1811,19 @@
       <c r="O50" s="14"/>
     </row>
     <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="17"/>
+      <c r="A51" s="18"/>
       <c r="B51" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="C51" s="21"/>
-      <c r="D51" s="21"/>
-      <c r="E51" s="21"/>
-      <c r="F51" s="21"/>
-      <c r="G51" s="21"/>
-      <c r="H51" s="21"/>
-      <c r="I51" s="21"/>
-      <c r="J51" s="21"/>
-      <c r="K51" s="21"/>
+      <c r="C51" s="22"/>
+      <c r="D51" s="22"/>
+      <c r="E51" s="22"/>
+      <c r="F51" s="22"/>
+      <c r="G51" s="22"/>
+      <c r="H51" s="22"/>
+      <c r="I51" s="22"/>
+      <c r="J51" s="22"/>
+      <c r="K51" s="22"/>
       <c r="L51" s="14" t="s">
         <v>6</v>
       </c>
@@ -1824,20 +1832,22 @@
       <c r="O51" s="14"/>
     </row>
   </sheetData>
-  <mergeCells count="34">
+  <mergeCells count="36">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:O1"/>
     <mergeCell ref="A3:A18"/>
-    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="C9:D9"/>
     <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="C13:E13"/>
     <mergeCell ref="C15:E15"/>
+    <mergeCell ref="C16:E16"/>
     <mergeCell ref="C18:E18"/>
     <mergeCell ref="A19:A38"/>
-    <mergeCell ref="F20:M20"/>
-    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="D20:M20"/>
     <mergeCell ref="E22:H22"/>
-    <mergeCell ref="H23:J23"/>
+    <mergeCell ref="D23:G23"/>
     <mergeCell ref="H24:J24"/>
     <mergeCell ref="H26:J26"/>
     <mergeCell ref="H27:J27"/>
